--- a/data/export/2026-10-06-浦东35路.xlsx
+++ b/data/export/2026-10-06-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -887,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1270,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1381,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1492,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1603,1117 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/19</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-06-浦东35路.xlsx
+++ b/data/export/2026-10-06-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC20"/>
+  <dimension ref="A1:AC31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +693,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>3/27</t>
         </is>
       </c>
     </row>
@@ -743,32 +751,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,33 +812,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>4/27</t>
         </is>
       </c>
     </row>
@@ -854,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -887,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,17 +931,17 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -931,13 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>1/27</t>
         </is>
       </c>
     </row>
@@ -998,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1072,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1076,32 +1100,36 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1109,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1133,33 +1161,37 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>2/27</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1302,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1363,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1413,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1474,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1524,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1585,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1635,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1696,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1714,7 +1746,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1807,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1825,7 +1857,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1918,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1936,7 +1968,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2029,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2047,7 +2079,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2140,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:11</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2158,7 +2190,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2251,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2269,7 +2301,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2362,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2380,7 +2412,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2473,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2491,7 +2523,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2552,7 +2584,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2602,7 +2634,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2695,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2713,7 +2745,1240 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/19</t>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A36993D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A67672D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:28</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>3/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>4/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>08:48</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>—/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>2/27</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-06-浦东35路.xlsx
+++ b/data/export/2026-10-06-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC31"/>
+  <dimension ref="A1:AC40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -446,10 +446,10 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,14 +946,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
           <t>125.0</t>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/27</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -989,32 +989,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1022,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1046,33 +1050,37 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1118,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>08:37</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
@@ -1137,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1186,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -1219,32 +1227,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1252,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1276,33 +1288,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1330,32 +1346,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1363,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1387,33 +1407,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1441,32 +1465,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -1474,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1498,33 +1526,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1552,32 +1584,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -1585,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1609,33 +1645,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1663,32 +1703,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1696,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1720,33 +1764,37 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1774,12 +1822,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq38推进至seq59，推进21站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1807,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1815,10 +1863,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q12" s="2" t="inlineStr"/>
-      <c r="R12" s="2" t="inlineStr"/>
-      <c r="S12" s="2" t="inlineStr"/>
-      <c r="T12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>物理seq22（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>07:58</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq22映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置物理seq38（站名待映射） ETA 20分钟参与校验</t>
+        </is>
+      </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
           <t>07:12</t>
@@ -1857,7 +1921,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1968,7 +2032,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -1996,32 +2060,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2029,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2053,33 +2121,37 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -2107,12 +2179,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq40推进至seq55，推进15站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2140,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:11</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2148,10 +2220,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q15" s="2" t="inlineStr"/>
-      <c r="R15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="inlineStr">
+        <is>
+          <t>08:16</t>
+        </is>
+      </c>
       <c r="S15" s="2" t="inlineStr"/>
-      <c r="T15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq23映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
           <t>07:24</t>
@@ -2190,7 +2274,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2301,7 +2385,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2446,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2412,7 +2496,7 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2523,7 +2607,7 @@
       <c r="AB18" s="2" t="inlineStr"/>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2634,7 +2718,7 @@
       <c r="AB19" s="2" t="inlineStr"/>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2779,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2745,7 +2829,7 @@
       <c r="AB20" s="2" t="inlineStr"/>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2890,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2856,7 +2940,7 @@
       <c r="AB21" s="2" t="inlineStr"/>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -2917,7 +3001,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2967,7 +3051,7 @@
       <c r="AB22" s="2" t="inlineStr"/>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3112,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3078,7 +3162,7 @@
       <c r="AB23" s="2" t="inlineStr"/>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3139,7 +3223,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3189,7 +3273,7 @@
       <c r="AB24" s="2" t="inlineStr"/>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3250,7 +3334,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3300,7 +3384,7 @@
       <c r="AB25" s="2" t="inlineStr"/>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3361,7 +3445,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3411,7 +3495,7 @@
       <c r="AB26" s="2" t="inlineStr"/>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3556,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3522,7 +3606,7 @@
       <c r="AB27" s="2" t="inlineStr"/>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3583,7 +3667,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3637,7 +3721,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>3/27</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3782,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3752,7 +3836,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/27</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -3813,7 +3897,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3863,7 +3947,7 @@
       <c r="AB30" s="2" t="inlineStr"/>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>—/27</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -3871,22 +3955,22 @@
       <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -3924,7 +4008,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3973,12 +4057,1043 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>126.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>2/27</t>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>8/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>8/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>8/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-06-浦东35路.xlsx
+++ b/data/export/2026-10-06-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC40"/>
+  <dimension ref="A1:AC47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq40推进至seq55，推进15站，达到≥2站确认条件</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq40推进至seq61，推进21站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2302,32 +2302,36 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -2335,7 +2339,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2359,33 +2363,37 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -2446,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2485,7 +2493,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2524,32 +2532,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -2557,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2581,33 +2593,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -2635,32 +2651,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2668,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2692,33 +2712,37 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -2746,32 +2770,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2779,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2803,33 +2831,37 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -2857,32 +2889,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -2890,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2914,33 +2950,37 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -2968,32 +3008,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3001,7 +3045,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3025,17 +3069,17 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
@@ -3045,13 +3089,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -3079,32 +3127,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -3112,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3136,17 +3188,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3156,13 +3208,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -3190,32 +3246,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3223,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3247,17 +3307,17 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3267,13 +3327,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -3334,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3445,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3556,7 +3620,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3667,7 +3731,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3721,7 +3785,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -3782,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3836,7 +3900,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -3897,7 +3961,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4008,7 +4072,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4062,7 +4126,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4123,7 +4187,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4177,7 +4241,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -4238,7 +4302,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4353,7 +4417,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4407,7 +4471,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4532,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4522,7 +4586,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -4583,7 +4647,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4637,7 +4701,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4698,7 +4762,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4809,7 +4873,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4863,7 +4927,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -4924,7 +4988,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4978,7 +5042,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -5039,7 +5103,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>09:21</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5093,7 +5157,804 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>13/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr"/>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>12/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr"/>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>17/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>138.0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>19/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-06-浦东35路.xlsx
+++ b/data/export/2026-10-06-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC47"/>
+  <dimension ref="A1:AC49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3203,7 +3203,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3256,12 +3256,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
@@ -3283,7 +3283,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3620,7 +3620,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -3961,7 +3961,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -4647,7 +4647,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4927,7 +4927,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -4988,7 +4988,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -5218,7 +5218,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5444,7 +5444,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5555,7 +5555,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5724,7 +5724,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -5785,7 +5785,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5958,6 +5958,236 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A15330A</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>127.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-06-浦东35路.xlsx
+++ b/data/export/2026-10-06-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC49"/>
+  <dimension ref="A1:AC53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2742,7 +2742,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3164,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3476,32 +3476,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3509,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3533,17 +3537,17 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3553,13 +3557,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -3587,32 +3595,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3620,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3644,33 +3656,37 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -3698,32 +3714,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:46</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3731,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3755,17 +3775,17 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -3775,7 +3795,7 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
@@ -3785,7 +3805,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -3813,32 +3833,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3846,7 +3870,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3870,17 +3894,17 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
@@ -3890,17 +3914,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -3928,32 +3952,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -3961,7 +3989,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3985,33 +4013,37 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB30" s="2" t="inlineStr"/>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -4039,32 +4071,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4072,7 +4108,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4096,17 +4132,17 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4116,17 +4152,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>125.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -4154,32 +4190,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4187,7 +4227,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4211,37 +4251,37 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -4269,32 +4309,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4302,7 +4346,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4326,37 +4370,37 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4384,32 +4428,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>136分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4417,7 +4465,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4441,17 +4489,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4461,17 +4509,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -4532,7 +4580,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4647,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4701,7 +4749,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -4729,12 +4777,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq49，推进11站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -4762,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4770,10 +4818,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q37" s="2" t="inlineStr"/>
-      <c r="R37" s="2" t="inlineStr"/>
-      <c r="S37" s="2" t="inlineStr"/>
-      <c r="T37" s="2" t="inlineStr"/>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq38（站名待映射） ETA 5分钟参与校验</t>
+        </is>
+      </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
           <t>09:38</t>
@@ -4873,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4988,7 +5052,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5042,7 +5106,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -5103,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5218,7 +5282,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5329,7 +5393,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5444,7 +5508,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5555,7 +5619,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5670,7 +5734,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5724,7 +5788,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -5785,7 +5849,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5900,7 +5964,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5954,7 +6018,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -6015,7 +6079,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6059,7 +6123,7 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
@@ -6069,7 +6133,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6194,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6188,6 +6252,466 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>20/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>125.5</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>14/28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-06-浦东35路.xlsx
+++ b/data/export/2026-10-06-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC53"/>
+  <dimension ref="A1:AC59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2021,18 +2021,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2101,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,12 +2145,12 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2339,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2383,17 +2387,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2458,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2498,13 +2502,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2577,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2608,17 +2616,17 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2688,7 +2696,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2732,12 +2740,12 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2807,7 +2815,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2861,7 +2869,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2934,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2980,7 +2988,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3053,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3084,14 +3092,14 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
           <t>128.0</t>
@@ -3099,7 +3107,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -3164,7 +3172,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3218,7 +3226,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -3337,7 +3345,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -3567,7 +3575,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3686,7 +3694,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3805,7 +3813,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -3924,7 +3932,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -3989,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4043,7 +4051,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4170,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4281,7 +4289,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -4346,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4400,7 +4408,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -4438,24 +4446,24 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>136分钟</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4465,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4514,12 +4522,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -4547,32 +4555,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:36</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4580,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4604,17 +4616,17 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
@@ -4624,17 +4636,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -4662,32 +4674,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -4695,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4719,32 +4735,32 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
@@ -4782,7 +4798,7 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq49，推进11站，达到≥2站确认条件</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq58，推进20站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -4810,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4865,7 +4881,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4904,32 +4920,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -4937,7 +4957,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4961,17 +4981,17 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4981,17 +5001,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -5019,32 +5039,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -5052,7 +5076,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5076,17 +5100,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5096,17 +5120,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>127.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -5134,32 +5158,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5167,7 +5195,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5191,17 +5219,17 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
@@ -5211,12 +5239,12 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5249,32 +5277,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5282,7 +5314,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5306,33 +5338,37 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB41" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -5360,32 +5396,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -5393,7 +5433,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5417,17 +5457,17 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5437,17 +5477,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -5475,32 +5515,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -5508,7 +5552,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5532,17 +5576,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5552,13 +5596,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB43" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -5586,32 +5634,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>120分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -5619,7 +5671,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5643,32 +5695,32 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5701,32 +5753,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5734,7 +5790,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5758,17 +5814,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5778,12 +5834,12 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5849,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5903,7 +5959,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -5964,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6018,7 +6074,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -6079,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6133,7 +6189,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6248,7 +6304,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -6309,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6363,7 +6419,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -6424,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6478,7 +6534,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -6539,7 +6595,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6593,7 +6649,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -6654,7 +6710,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6708,7 +6764,689 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>16/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A79307D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr"/>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>9/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>126.5</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>6/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>17/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr"/>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>122.0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-06-浦东35路.xlsx
+++ b/data/export/2026-10-06-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC59"/>
+  <dimension ref="A1:AC65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2815,7 +2815,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2859,17 +2859,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2973,17 +2973,17 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3211,22 +3211,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3679,22 +3679,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -5406,24 +5406,24 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5433,7 +5433,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>131.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -5644,24 +5644,24 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>120分钟</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5720,7 +5720,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5872,32 +5872,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5905,7 +5909,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5929,17 +5933,17 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5949,17 +5953,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>125.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -5987,32 +5991,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -6020,7 +6028,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6044,32 +6052,32 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>138.0</t>
+          <t>135.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6135,7 +6143,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6217,32 +6225,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -6250,7 +6262,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6274,37 +6286,37 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>126.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -6365,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6447,32 +6459,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6480,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6504,37 +6520,37 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6611,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6710,7 +6726,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6749,7 +6765,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6825,7 +6841,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6936,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7051,7 +7067,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7166,7 +7182,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7220,7 +7236,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7297,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7392,7 +7408,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7441,12 +7457,698 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>123.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
           <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr"/>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>131.5</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>17/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>126.5</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>6/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>135.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>24/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>20/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>131.0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>16/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-06-浦东35路.xlsx
+++ b/data/export/2026-10-06-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC65"/>
+  <dimension ref="A1:AC70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>125.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3097,17 +3097,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3689,7 +3689,7 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3759,7 +3759,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3798,22 +3798,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4041,17 +4041,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4279,17 +4279,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>125.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4750,22 +4750,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4826,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -5249,7 +5249,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5433,7 +5433,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6110,32 +6110,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6143,7 +6147,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6167,37 +6171,37 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6266,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6344,32 +6348,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -6377,7 +6385,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6401,17 +6409,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6421,17 +6429,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>124.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -6469,12 +6477,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
@@ -6496,7 +6504,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6545,7 +6553,7 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6578,32 +6586,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6611,7 +6623,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6635,17 +6647,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6655,12 +6667,12 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>125.5</t>
+          <t>125.3</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6693,32 +6705,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6726,7 +6742,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6750,17 +6766,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6770,17 +6786,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -6808,12 +6824,12 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq38推进至seq52，推进14站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -6841,7 +6857,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6849,10 +6865,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q54" s="2" t="inlineStr"/>
-      <c r="R54" s="2" t="inlineStr"/>
-      <c r="S54" s="2" t="inlineStr"/>
-      <c r="T54" s="2" t="inlineStr"/>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>物理seq22（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>13:24</t>
+        </is>
+      </c>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq22映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±7分钟；反向位置物理seq38（站名待映射） ETA 8分钟参与校验</t>
+        </is>
+      </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
           <t>12:28</t>
@@ -6919,32 +6951,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6952,7 +6988,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6976,17 +7012,17 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
@@ -6996,17 +7032,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -7034,32 +7070,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -7067,7 +7107,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7091,37 +7131,37 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>129.3</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -7182,7 +7222,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7297,7 +7337,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7336,7 +7376,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7408,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7523,7 +7563,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7634,7 +7674,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7749,7 +7789,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7864,7 +7904,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7979,7 +8019,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8028,7 +8068,7 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.5</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8041,22 +8081,22 @@
       <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A15330A</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>14:35</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -8094,7 +8134,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8108,47 +8148,618 @@
       <c r="T65" s="2" t="inlineStr"/>
       <c r="U65" s="2" t="inlineStr">
         <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>128.7</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>10/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A73927D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
           <t>14:35</t>
         </is>
       </c>
-      <c r="V65" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W65" s="2" t="inlineStr">
+      <c r="W66" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X65" s="2" t="inlineStr">
+      <c r="X66" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y65" s="2" t="inlineStr">
+      <c r="Y66" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z65" s="2" t="inlineStr">
+      <c r="Z66" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>129.7</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>14/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB65" s="2" t="inlineStr">
-        <is>
-          <t>131.0</t>
-        </is>
-      </c>
-      <c r="AC65" s="2" t="inlineStr">
-        <is>
-          <t>16/28</t>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>129.5</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>13/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>129.3</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>12/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>22/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr"/>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-06-浦东35路.xlsx
+++ b/data/export/2026-10-06-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC70"/>
+  <dimension ref="A1:AC75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
           <t>134.0</t>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1915,13 +1915,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1986,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2026,17 +2030,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2140,14 +2144,14 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
           <t>130.0</t>
@@ -2155,7 +2159,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2267,18 +2271,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2351,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2387,12 +2395,12 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2512,7 +2520,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2621,17 +2629,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>123.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -2750,7 +2758,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -2869,7 +2877,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2988,7 +2996,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>26/28</t>
         </is>
       </c>
     </row>
@@ -3053,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3107,7 +3115,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3216,17 +3224,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3353,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3529,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3560,14 +3568,14 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
           <t>132.0</t>
@@ -3575,7 +3583,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -3640,7 +3648,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3694,7 +3702,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3767,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3813,7 +3821,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -3878,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3932,7 +3940,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4059,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4243,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4289,7 +4297,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -4408,7 +4416,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -4473,7 +4481,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4527,7 +4535,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -4711,7 +4719,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4765,7 +4773,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -4826,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4881,7 +4889,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4957,7 +4965,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4996,14 +5004,14 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
           <t>134.0</t>
@@ -5011,7 +5019,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5203,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5234,14 +5242,14 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
           <t>130.0</t>
@@ -5249,7 +5257,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5322,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5358,17 +5366,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5441,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5477,12 +5485,12 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5606,7 +5614,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -5671,7 +5679,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5715,17 +5723,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>123.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -5844,7 +5852,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -5963,7 +5971,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -6028,7 +6036,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6082,7 +6090,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>26/28</t>
         </is>
       </c>
     </row>
@@ -6147,7 +6155,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6201,7 +6209,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -6266,7 +6274,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6310,17 +6318,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -6439,7 +6447,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -6504,7 +6512,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6558,7 +6566,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -6677,7 +6685,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -6742,7 +6750,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6796,7 +6804,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -6829,7 +6837,7 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq38推进至seq52，推进14站，达到≥2站确认条件</t>
+          <t>原方向在全程33%处后消失；随后反向物理轨迹由seq38推进至seq58，推进20站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -6857,7 +6865,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6912,7 +6920,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6988,7 +6996,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7042,7 +7050,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -7092,12 +7100,12 @@
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -7107,7 +7115,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7161,7 +7169,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -7189,32 +7197,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -7222,7 +7234,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7246,17 +7258,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7266,17 +7278,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -7304,32 +7316,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -7337,7 +7353,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7361,17 +7377,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7381,13 +7397,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB58" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -7415,32 +7435,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -7448,7 +7472,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7472,17 +7496,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7492,17 +7516,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>123.0</t>
+          <t>123.7</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -7530,32 +7554,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -7563,7 +7591,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7587,33 +7615,37 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB60" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -7641,32 +7673,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -7674,7 +7710,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7698,17 +7734,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7718,12 +7754,12 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>131.5</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7756,32 +7792,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>134分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -7789,7 +7829,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7813,17 +7853,17 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
@@ -7833,17 +7873,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>126.5</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7944,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7958,7 +7998,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>26/28</t>
         </is>
       </c>
     </row>
@@ -8019,7 +8059,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8073,7 +8113,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -8134,7 +8174,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8188,7 +8228,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -8249,7 +8289,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8303,7 +8343,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8404,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8418,7 +8458,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -8479,7 +8519,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8533,7 +8573,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -8594,7 +8634,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8648,7 +8688,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -8656,22 +8696,22 @@
       <c r="A70" s="2" t="inlineStr"/>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A79307D</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>15:25</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -8704,12 +8744,12 @@
       <c r="M70" s="2" t="inlineStr"/>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8723,7 +8763,7 @@
       <c r="T70" s="2" t="inlineStr"/>
       <c r="U70" s="2" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="V70" s="2" t="inlineStr">
@@ -8760,6 +8800,581 @@
       <c r="AC70" s="2" t="inlineStr">
         <is>
           <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>24/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>132.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>21/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>130.0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>19/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>129.0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>12/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-06-浦东35路.xlsx
+++ b/data/export/2026-10-06-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC75"/>
+  <dimension ref="A1:AC82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,14 +946,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
           <t>128.5</t>
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,14 +1422,14 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
           <t>128.5</t>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,14 +1660,14 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
           <t>127.5</t>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2400,12 +2400,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3229,12 +3229,12 @@
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3692,12 +3692,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3811,17 +3811,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4163,14 +4163,14 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
           <t>128.5</t>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -4243,7 +4243,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4287,17 +4287,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -4362,7 +4362,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4639,14 +4639,14 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
           <t>128.5</t>
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5123,14 +5123,14 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
           <t>127.5</t>
@@ -5138,7 +5138,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5257,7 +5257,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5490,12 +5490,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5837,7 +5837,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6080,12 +6080,12 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6155,7 +6155,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6199,17 +6199,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6323,12 +6323,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6432,7 +6432,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6556,12 +6556,12 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6670,7 +6670,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6750,7 +6750,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6794,17 +6794,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -6865,7 +6865,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7234,7 +7234,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7273,7 +7273,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7288,7 +7288,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -7353,7 +7353,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7564,24 +7564,24 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>129分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -7683,24 +7683,24 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7710,7 +7710,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7759,12 +7759,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -7802,24 +7802,24 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:56</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>134分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7829,7 +7829,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -7911,32 +7911,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -7944,7 +7948,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7968,17 +7972,17 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
@@ -7988,12 +7992,12 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>135.0</t>
+          <t>136.7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8026,32 +8030,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8059,7 +8067,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8083,17 +8091,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8103,12 +8111,12 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>132.5</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8141,32 +8149,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8174,7 +8186,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8198,17 +8210,17 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
@@ -8218,17 +8230,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -8256,32 +8268,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8289,7 +8305,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8313,17 +8329,17 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
@@ -8333,17 +8349,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>129.7</t>
+          <t>130.5</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -8404,7 +8420,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8519,7 +8535,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8634,7 +8650,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8749,7 +8765,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8860,7 +8876,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8975,7 +8991,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9090,7 +9106,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9205,7 +9221,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9259,7 +9275,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -9320,7 +9336,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9369,12 +9385,817 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>127.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>7/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>16:11</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>128.5</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>10/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>133.0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>23/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>128.5</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>10/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>124.5</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>125.3</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>6/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>127.5</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>8/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A62981D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>128.5</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>10/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-06-浦东35路.xlsx
+++ b/data/export/2026-10-06-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC82"/>
+  <dimension ref="A1:AC89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>130.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1194,12 +1194,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,12 +1784,12 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2624,7 +2624,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3353,7 +3353,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3816,7 +3816,7 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.8</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3925,22 +3925,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>130.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -4362,7 +4362,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4520,22 +4520,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4763,17 +4763,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5257,7 +5257,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5679,7 +5679,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -6155,7 +6155,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6274,7 +6274,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6750,7 +6750,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -6865,7 +6865,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7159,17 +7159,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7472,7 +7472,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -7829,7 +7829,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -8159,24 +8159,24 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>130分钟</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8235,7 +8235,7 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>128.8</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8278,24 +8278,24 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>16:48</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:41</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8354,12 +8354,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>130.5</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -8387,32 +8387,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:57</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8420,7 +8424,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8444,37 +8448,37 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>130.3</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>16/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -8502,32 +8506,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -8535,7 +8543,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8559,17 +8567,17 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
@@ -8579,17 +8587,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>129.3</t>
+          <t>130.8</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -8617,32 +8625,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:28</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>138分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8650,7 +8662,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8674,37 +8686,37 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA69" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>135.3</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>25/28</t>
         </is>
       </c>
     </row>
@@ -8732,12 +8744,12 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq62，推进24站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -8765,7 +8777,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8773,10 +8785,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q70" s="2" t="inlineStr"/>
-      <c r="R70" s="2" t="inlineStr"/>
-      <c r="S70" s="2" t="inlineStr"/>
-      <c r="T70" s="2" t="inlineStr"/>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="S70" s="2" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
+      <c r="T70" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±5分钟；反向位置物理seq38（站名待映射） ETA 8分钟参与校验</t>
+        </is>
+      </c>
       <c r="U70" s="2" t="inlineStr">
         <is>
           <t>15:22</t>
@@ -8876,7 +8904,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8915,7 +8943,7 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
@@ -8958,32 +8986,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -8991,7 +9023,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9015,17 +9047,17 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
@@ -9035,12 +9067,12 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>133.3</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
@@ -9106,7 +9138,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9221,7 +9253,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9275,7 +9307,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -9336,7 +9368,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9451,7 +9483,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9566,7 +9598,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9681,7 +9713,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9796,7 +9828,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9911,7 +9943,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10026,7 +10058,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10141,7 +10173,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10199,6 +10231,811 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>124.0</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>3/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>123.7</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>130.3</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>18/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A68895D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>128.0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>9/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>135.3</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>25/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A02316D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>121.0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>5/28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-06-浦东35路.xlsx
+++ b/data/export/2026-10-06-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC89"/>
+  <dimension ref="A1:AC92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2040,7 +2040,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2149,17 +2149,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2276,17 +2276,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2390,14 +2390,14 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
           <t>130.7</t>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2748,17 +2748,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3940,7 +3940,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -4362,7 +4362,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5004,7 +5004,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5247,17 +5247,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5480,14 +5480,14 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
           <t>130.7</t>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5679,7 +5679,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5842,17 +5842,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -5917,7 +5917,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6865,7 +6865,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6920,7 +6920,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7288,7 +7288,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -7353,7 +7353,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7472,7 +7472,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7635,17 +7635,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7749,14 +7749,14 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
           <t>130.7</t>
@@ -7764,7 +7764,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -7829,7 +7829,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -8121,7 +8121,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -8240,7 +8240,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -8662,7 +8662,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8777,7 +8777,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8832,7 +8832,7 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -9023,7 +9023,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9062,7 +9062,7 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
@@ -9105,32 +9105,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9138,7 +9142,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9162,17 +9166,17 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
@@ -9182,17 +9186,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -9220,32 +9224,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9253,7 +9261,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9277,17 +9285,17 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
@@ -9297,17 +9305,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>130.0</t>
+          <t>130.7</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -9335,32 +9343,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:18</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>137分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -9368,7 +9380,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9392,17 +9404,17 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
@@ -9412,17 +9424,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>127.0</t>
+          <t>132.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -9483,7 +9495,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9537,7 +9549,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -9565,32 +9577,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -9598,7 +9614,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9622,17 +9638,17 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
@@ -9642,17 +9658,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>133.0</t>
+          <t>132.3</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>22/28</t>
         </is>
       </c>
     </row>
@@ -9713,7 +9729,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9767,7 +9783,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -9828,7 +9844,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9943,7 +9959,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10058,7 +10074,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10112,7 +10128,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -10173,7 +10189,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10227,7 +10243,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -10288,7 +10304,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10403,7 +10419,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10518,7 +10534,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10572,7 +10588,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -10633,7 +10649,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10687,7 +10703,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -10748,7 +10764,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10863,7 +10879,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10925,22 +10941,22 @@
       <c r="A89" s="2" t="inlineStr"/>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>沪A53893D</t>
+          <t>沪A79307D</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>18:20</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -10973,12 +10989,12 @@
       <c r="M89" s="2" t="inlineStr"/>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10992,47 +11008,388 @@
       <c r="T89" s="2" t="inlineStr"/>
       <c r="U89" s="2" t="inlineStr">
         <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr"/>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
           <t>18:20</t>
         </is>
       </c>
-      <c r="V89" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W89" s="2" t="inlineStr">
+      <c r="W90" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X89" s="2" t="inlineStr">
+      <c r="X90" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y89" s="2" t="inlineStr">
+      <c r="Y90" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z89" s="2" t="inlineStr">
+      <c r="Z90" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA89" s="2" t="inlineStr">
+      <c r="AA90" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB89" s="2" t="inlineStr">
+      <c r="AB90" s="2" t="inlineStr">
         <is>
           <t>125.0</t>
         </is>
       </c>
-      <c r="AC89" s="2" t="inlineStr">
+      <c r="AC90" s="2" t="inlineStr">
         <is>
           <t>5/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A65668D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>130.7</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>18/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>133.3</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>24/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-06-浦东35路.xlsx
+++ b/data/export/2026-10-06-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC92"/>
+  <dimension ref="A1:AC96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>130.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2351,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2753,12 +2753,12 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4163,22 +4163,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -4362,7 +4362,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5019,7 +5019,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5242,22 +5242,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>130.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5679,7 +5679,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5847,12 +5847,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -5917,7 +5917,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6274,7 +6274,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6865,7 +6865,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7035,7 +7035,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -7234,7 +7234,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7472,7 +7472,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -7829,7 +7829,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8777,7 +8777,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -9023,7 +9023,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9077,7 +9077,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>24/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -9142,7 +9142,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9181,7 +9181,7 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9234,24 +9234,24 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>18:13</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>132分钟</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
@@ -9261,7 +9261,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9300,22 +9300,22 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA74" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>130.3</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -9353,24 +9353,24 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>18:18</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>137分钟</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9429,12 +9429,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>132.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -9462,32 +9462,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9495,7 +9499,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9519,37 +9523,37 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA76" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -9587,12 +9591,12 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
@@ -9614,7 +9618,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9663,12 +9667,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>132.3</t>
+          <t>132.7</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>22/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -9729,7 +9733,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9844,7 +9848,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9959,7 +9963,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10074,7 +10078,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10189,7 +10193,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10304,7 +10308,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10419,7 +10423,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10534,7 +10538,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10649,7 +10653,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10764,7 +10768,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10879,7 +10883,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10994,7 +10998,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11105,7 +11109,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11167,22 +11171,22 @@
       <c r="A91" s="2" t="inlineStr"/>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>18:40</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -11215,12 +11219,12 @@
       <c r="M91" s="2" t="inlineStr"/>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11234,7 +11238,7 @@
       <c r="T91" s="2" t="inlineStr"/>
       <c r="U91" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="V91" s="2" t="inlineStr">
@@ -11259,22 +11263,22 @@
       </c>
       <c r="Z91" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>129.0</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -11282,7 +11286,7 @@
       <c r="A92" s="2" t="inlineStr"/>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -11292,7 +11296,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -11330,12 +11334,12 @@
       <c r="M92" s="2" t="inlineStr"/>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:01</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11349,47 +11353,507 @@
       <c r="T92" s="2" t="inlineStr"/>
       <c r="U92" s="2" t="inlineStr">
         <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>130.7</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>19/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>129.5</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>14/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
           <t>19:00</t>
         </is>
       </c>
-      <c r="V92" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W92" s="2" t="inlineStr">
+      <c r="W94" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X92" s="2" t="inlineStr">
+      <c r="X94" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y92" s="2" t="inlineStr">
+      <c r="Y94" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z92" s="2" t="inlineStr">
+      <c r="Z94" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA92" s="2" t="inlineStr">
+      <c r="AA94" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB92" s="2" t="inlineStr">
+      <c r="AB94" s="2" t="inlineStr">
         <is>
           <t>133.3</t>
         </is>
       </c>
-      <c r="AC92" s="2" t="inlineStr">
-        <is>
-          <t>24/28</t>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>23/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>128.7</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>11/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>130.3</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>17/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-06-浦东35路.xlsx
+++ b/data/export/2026-10-06-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC96"/>
+  <dimension ref="A1:AC101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>130.3</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>125.3</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2030,17 +2030,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2510,17 +2510,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3583,7 +3583,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3930,17 +3930,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>130.3</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4044,22 +4044,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>123.7</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -4362,7 +4362,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4406,17 +4406,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>125.3</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4639,22 +4639,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -4773,7 +4773,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5366,17 +5366,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5604,17 +5604,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -5679,7 +5679,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5837,7 +5837,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6432,22 +6432,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>123.7</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6675,17 +6675,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>125.3</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -6865,7 +6865,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -7169,7 +7169,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7278,17 +7278,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -7353,7 +7353,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7472,7 +7472,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7630,7 +7630,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7710,7 +7710,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -7829,7 +7829,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7987,7 +7987,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -8240,7 +8240,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8468,17 +8468,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>130.3</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -8597,7 +8597,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -8662,7 +8662,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8777,7 +8777,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -9023,7 +9023,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9142,7 +9142,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9196,7 +9196,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -9261,7 +9261,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9380,7 +9380,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9419,7 +9419,7 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9499,7 +9499,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9553,7 +9553,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -9603,12 +9603,12 @@
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9700,32 +9700,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>132分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -9733,7 +9737,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9757,37 +9761,37 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA78" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>129.7</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -9815,32 +9819,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -9848,7 +9856,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9872,37 +9880,37 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA79" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>124.5</t>
+          <t>123.7</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -9930,32 +9938,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9963,7 +9975,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9987,17 +9999,17 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
@@ -10007,17 +10019,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>125.3</t>
+          <t>125.5</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>6/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -10045,32 +10057,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -10078,7 +10094,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10102,17 +10118,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10122,17 +10138,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>127.5</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>7/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -10160,32 +10176,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -10193,7 +10213,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10217,17 +10237,17 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
@@ -10237,17 +10257,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>128.5</t>
+          <t>126.3</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -10275,32 +10295,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:51</t>
@@ -10308,7 +10332,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10332,17 +10356,17 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
@@ -10352,17 +10376,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>124.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>3/28</t>
+          <t>6/28</t>
         </is>
       </c>
     </row>
@@ -10423,7 +10447,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10505,32 +10529,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10538,7 +10566,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10562,17 +10590,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10582,17 +10610,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>130.3</t>
+          <t>131.0</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -10653,7 +10681,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10707,7 +10735,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -10768,7 +10796,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10883,7 +10911,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10998,7 +11026,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11109,7 +11137,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11163,7 +11191,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>5/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -11224,7 +11252,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11278,7 +11306,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -11339,7 +11367,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11393,7 +11421,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -11454,7 +11482,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11508,7 +11536,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -11569,7 +11597,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11631,22 +11659,22 @@
       <c r="A95" s="2" t="inlineStr"/>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -11679,12 +11707,12 @@
       <c r="M95" s="2" t="inlineStr"/>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11698,7 +11726,7 @@
       <c r="T95" s="2" t="inlineStr"/>
       <c r="U95" s="2" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="V95" s="2" t="inlineStr">
@@ -11733,12 +11761,12 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>123.7</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -11746,22 +11774,22 @@
       <c r="A96" s="2" t="inlineStr"/>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>19:20</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -11794,12 +11822,12 @@
       <c r="M96" s="2" t="inlineStr"/>
       <c r="N96" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:11</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11813,47 +11841,622 @@
       <c r="T96" s="2" t="inlineStr"/>
       <c r="U96" s="2" t="inlineStr">
         <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>128.7</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>10/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
           <t>19:20</t>
         </is>
       </c>
-      <c r="V96" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W96" s="2" t="inlineStr">
+      <c r="W97" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X96" s="2" t="inlineStr">
+      <c r="X97" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y96" s="2" t="inlineStr">
+      <c r="Y97" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z96" s="2" t="inlineStr">
+      <c r="Z97" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA96" s="2" t="inlineStr">
+      <c r="AA97" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB96" s="2" t="inlineStr">
+      <c r="AB97" s="2" t="inlineStr">
         <is>
           <t>130.3</t>
         </is>
       </c>
-      <c r="AC96" s="2" t="inlineStr">
+      <c r="AC97" s="2" t="inlineStr">
         <is>
           <t>17/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>134.0</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>24/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>129.7</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>14/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>132.7</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>21/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>136.7</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>26/28</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-06-浦东35路.xlsx
+++ b/data/export/2026-10-06-浦东35路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC101"/>
+  <dimension ref="A1:AC104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -837,12 +837,12 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -2105,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2405,7 +2405,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>123.7</t>
+          <t>123.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3105,17 +3105,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3224,17 +3224,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3821,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3886,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4059,7 +4059,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4525,17 +4525,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4965,7 +4965,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5257,7 +5257,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5679,7 +5679,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5723,12 +5723,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>123.7</t>
+          <t>123.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5956,12 +5956,12 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6318,17 +6318,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6447,7 +6447,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -6865,7 +6865,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7040,17 +7040,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -7169,7 +7169,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -7472,7 +7472,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>123.7</t>
+          <t>123.2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7710,7 +7710,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -7829,7 +7829,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8240,7 +8240,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>13/28</t>
         </is>
       </c>
     </row>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8473,12 +8473,12 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -8597,7 +8597,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>20/28</t>
         </is>
       </c>
     </row>
@@ -8662,7 +8662,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8706,17 +8706,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -8777,7 +8777,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -9023,7 +9023,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9142,7 +9142,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9186,17 +9186,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -9261,7 +9261,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9315,7 +9315,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -9380,7 +9380,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9499,7 +9499,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9553,7 +9553,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9737,7 +9737,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9910,7 +9910,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -10094,7 +10094,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10133,7 +10133,7 @@
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
@@ -10332,7 +10332,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10371,7 +10371,7 @@
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
@@ -10414,32 +10414,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:42</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -10447,7 +10451,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10471,17 +10475,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10491,12 +10495,12 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>123.7</t>
+          <t>123.2</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
@@ -10539,24 +10543,24 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>19:53</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>133分钟</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N85" s="2" t="inlineStr">
@@ -10566,7 +10570,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10615,12 +10619,12 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>131.0</t>
+          <t>130.2</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>20/28</t>
+          <t>17/28</t>
         </is>
       </c>
     </row>
@@ -10648,32 +10652,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:31</t>
@@ -10681,7 +10689,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10705,17 +10713,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10725,17 +10733,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>128.5</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>9/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -10763,32 +10771,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>130分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10796,7 +10808,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10820,17 +10832,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10840,17 +10852,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>135.3</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>25/28</t>
+          <t>24/28</t>
         </is>
       </c>
     </row>
@@ -10993,12 +11005,12 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程36%处后消失；随后反向物理轨迹由seq38推进至seq63，推进25站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -11026,7 +11038,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11034,10 +11046,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q89" s="2" t="inlineStr"/>
-      <c r="R89" s="2" t="inlineStr"/>
-      <c r="S89" s="2" t="inlineStr"/>
-      <c r="T89" s="2" t="inlineStr"/>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>物理seq24（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr">
+        <is>
+          <t>19:04</t>
+        </is>
+      </c>
+      <c r="S89" s="2" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
+      <c r="T89" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq24映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±8分钟；反向位置物理seq38（站名待映射） ETA 8分钟参与校验</t>
+        </is>
+      </c>
       <c r="U89" s="2" t="inlineStr">
         <is>
           <t>18:12</t>
@@ -11104,32 +11132,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -11137,7 +11169,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11161,27 +11193,27 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="AA90" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
@@ -11219,32 +11251,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>124分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11252,7 +11288,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11276,17 +11312,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11296,17 +11332,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>129.0</t>
+          <t>127.3</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>12/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -11367,7 +11403,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11421,7 +11457,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -11449,32 +11485,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:57</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11482,7 +11522,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11506,17 +11546,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11526,17 +11566,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>129.5</t>
+          <t>128.7</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>13/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -11597,7 +11637,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11712,7 +11752,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11766,7 +11806,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -11827,7 +11867,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:11</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11881,7 +11921,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>11/28</t>
         </is>
       </c>
     </row>
@@ -11942,7 +11982,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11996,7 +12036,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>18/28</t>
         </is>
       </c>
     </row>
@@ -12057,7 +12097,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12172,7 +12212,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12287,7 +12327,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12402,7 +12442,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12460,6 +12500,351 @@
         </is>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>127.3</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>8/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>6/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A53893D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>20:21</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>125.0</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-06-浦东35路.xlsx
+++ b/data/export/2026-10-06-浦东35路.xlsx
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>126.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>131.8</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2149,17 +2149,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>130.3</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2395,17 +2395,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>131.8</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3110,12 +3110,12 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -3353,7 +3353,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3578,12 +3578,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -3702,7 +3702,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4005,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4124,7 +4124,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4168,17 +4168,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>126.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5009,17 +5009,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>131.8</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5247,17 +5247,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>130.3</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -5441,7 +5441,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5485,17 +5485,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -5560,7 +5560,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>131.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6036,7 +6036,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6328,7 +6328,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -6393,7 +6393,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -7591,7 +7591,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7710,7 +7710,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7754,17 +7754,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -7883,7 +7883,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>21/28</t>
+          <t>23/28</t>
         </is>
       </c>
     </row>
@@ -8359,7 +8359,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>15/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -8478,7 +8478,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -9023,7 +9023,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9067,17 +9067,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>131.8</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -9142,7 +9142,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9191,12 +9191,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -9261,7 +9261,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9305,17 +9305,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>130.3</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -9380,7 +9380,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9499,7 +9499,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9543,17 +9543,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>126.8</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9662,12 +9662,12 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>131.8</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9737,7 +9737,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9791,7 +9791,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -9856,7 +9856,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -10332,7 +10332,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10624,7 +10624,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>17/28</t>
+          <t>19/28</t>
         </is>
       </c>
     </row>
@@ -10743,7 +10743,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>10/28</t>
+          <t>12/28</t>
         </is>
       </c>
     </row>
@@ -11169,7 +11169,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11261,24 +11261,24 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>124分钟</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N91" s="2" t="inlineStr">
@@ -11288,7 +11288,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11337,12 +11337,12 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>127.3</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -11370,32 +11370,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:46</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -11403,7 +11407,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11427,17 +11431,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11447,17 +11451,17 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>130.7</t>
+          <t>129.5</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>19/28</t>
+          <t>14/28</t>
         </is>
       </c>
     </row>
@@ -11495,24 +11499,24 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>20:57</t>
+          <t>20:56</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>127分钟</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -11522,7 +11526,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11571,12 +11575,12 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>128.3</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>10/28</t>
         </is>
       </c>
     </row>
@@ -11604,32 +11608,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:07</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -11637,7 +11645,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11661,17 +11669,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11681,17 +11689,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>133.3</t>
+          <t>131.8</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>23/28</t>
+          <t>21/28</t>
         </is>
       </c>
     </row>
@@ -11719,12 +11727,12 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程43%处后消失；随后反向物理轨迹由seq28推进至seq62，推进34站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
@@ -11752,7 +11760,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11760,10 +11768,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q95" s="2" t="inlineStr"/>
-      <c r="R95" s="2" t="inlineStr"/>
-      <c r="S95" s="2" t="inlineStr"/>
-      <c r="T95" s="2" t="inlineStr"/>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>物理seq28（站名待映射）</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr">
+        <is>
+          <t>19:52</t>
+        </is>
+      </c>
+      <c r="S95" s="2" t="inlineStr">
+        <is>
+          <t>20:01</t>
+        </is>
+      </c>
+      <c r="T95" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq28映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="U95" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -11834,32 +11858,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:16</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>121分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11867,7 +11895,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11891,17 +11919,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11911,17 +11939,17 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>128.7</t>
+          <t>126.8</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>11/28</t>
+          <t>8/28</t>
         </is>
       </c>
     </row>
@@ -11949,32 +11977,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:29</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -11982,7 +12014,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -12006,17 +12038,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -12026,17 +12058,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>130.3</t>
+          <t>130.0</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>18/28</t>
+          <t>16/28</t>
         </is>
       </c>
     </row>
@@ -12097,7 +12129,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12212,7 +12244,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12266,7 +12298,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>14/28</t>
+          <t>15/28</t>
         </is>
       </c>
     </row>
@@ -12294,32 +12326,36 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:49</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -12327,7 +12363,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12351,17 +12387,17 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
@@ -12371,12 +12407,12 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>132.7</t>
+          <t>131.8</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
@@ -12442,7 +12478,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12557,7 +12593,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12611,7 +12647,7 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>8/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -12672,7 +12708,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12787,7 +12823,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
